--- a/experiment/HAT_2CH_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/HAT_2CH_bestx4/Test/results-Set14/Set14.xlsx
@@ -455,7 +455,7 @@
         <v>23.05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5363</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.37</v>
+        <v>26.38</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7619</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.35</v>
+        <v>25.36</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6368</v>
+        <v>0.6369</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.23</v>
+        <v>26.25</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5766</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.52</v>
+        <v>23.54</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7385</v>
+        <v>0.7389</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.94</v>
+        <v>32.96</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7962</v>
+        <v>0.7964</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.35</v>
+        <v>28.36</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8229</v>
+        <v>0.8232</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.66</v>
+        <v>33.6</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9197</v>
+        <v>0.9187</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>32.65</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8673</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.35</v>
+        <v>27.34</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7502</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.13</v>
+        <v>33.15</v>
       </c>
       <c r="C12" t="n">
         <v>0.9459</v>
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="C14" t="n">
-        <v>0.952</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.47</v>
+        <v>27.49</v>
       </c>
       <c r="C15" t="n">
         <v>0.7801</v>
@@ -637,7 +637,7 @@
         <v>28.66</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7833</v>
+        <v>0.7832</v>
       </c>
     </row>
   </sheetData>
